--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PUTNAM LAB\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B360CB-9B83-471B-9DE5-EFDBD1B366A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30F00EC-61CE-4FE1-A277-F752CF72C318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -213,7 +213,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,8 +373,14 @@
       <name val="Lucida Grande"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Console"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -554,8 +560,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -670,15 +682,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -724,7 +727,7 @@
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -733,7 +736,12 @@
     <xf numFmtId="2" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -793,9 +801,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -833,7 +841,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -939,7 +947,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1081,7 +1089,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1089,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -4470,7 +4478,7 @@
         <v>2224.4699999999998</v>
       </c>
       <c r="D162" s="1">
-        <f t="shared" ref="D162:D181" si="20">100*(B162-C162)/C162</f>
+        <f t="shared" ref="D162:D183" si="20">100*(B162-C162)/C162</f>
         <v>-2.1396062085382019</v>
       </c>
       <c r="E162" s="1">
@@ -4774,7 +4782,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="15.6">
+    <row r="177" spans="1:15" ht="15.6">
       <c r="A177" s="5">
         <v>20251114</v>
       </c>
@@ -4795,7 +4803,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="15.6">
+    <row r="178" spans="1:15" ht="15.6">
       <c r="A178" s="5">
         <v>20251216</v>
       </c>
@@ -4815,8 +4823,9 @@
       <c r="F178" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" ht="15.6">
+      <c r="O178" s="6"/>
+    </row>
+    <row r="179" spans="1:15" ht="15.6">
       <c r="A179" s="5">
         <v>20251216</v>
       </c>
@@ -4836,8 +4845,9 @@
       <c r="F179" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" ht="15.6">
+      <c r="O179" s="7"/>
+    </row>
+    <row r="180" spans="1:15" ht="15.6">
       <c r="A180" s="5">
         <v>20251216</v>
       </c>
@@ -4858,7 +4868,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="15.6">
+    <row r="181" spans="1:15" ht="15.6">
       <c r="A181" s="5">
         <v>20251216</v>
       </c>
@@ -4879,8 +4889,47 @@
         <v>57</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
-      <c r="A183" s="6"/>
+    <row r="182" spans="1:15" ht="15.6">
+      <c r="A182" s="5">
+        <v>20260603</v>
+      </c>
+      <c r="B182">
+        <v>2123.4549999999999</v>
+      </c>
+      <c r="C182" s="1">
+        <v>2224.4699999999998</v>
+      </c>
+      <c r="D182" s="1">
+        <f t="shared" si="20"/>
+        <v>-4.5410816958646274</v>
+      </c>
+      <c r="E182" s="1">
+        <v>180</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" ht="15.6">
+      <c r="A183" s="5">
+        <v>20260603</v>
+      </c>
+      <c r="B183">
+        <v>2111.1860000000001</v>
+      </c>
+      <c r="C183" s="1">
+        <v>2224.4699999999998</v>
+      </c>
+      <c r="D183" s="1">
+        <f t="shared" si="20"/>
+        <v>-5.0926288059627538</v>
+      </c>
+      <c r="E183" s="1">
+        <v>180</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>

--- a/Data/CRMAccuracyData.xlsx
+++ b/Data/CRMAccuracyData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PUTNAM LAB\Titrator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30F00EC-61CE-4FE1-A277-F752CF72C318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129C0479-2041-49E2-BF32-6B330D67C217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>CRM180_opened20251114_PP</t>
+  </si>
+  <si>
+    <t>CRM180_opened20260603_PPJH</t>
   </si>
 </sst>
 </file>
@@ -801,9 +804,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -841,7 +844,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -947,7 +950,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1089,7 +1092,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1097,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O183"/>
+  <dimension ref="A1:O185"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -4478,7 +4481,7 @@
         <v>2224.4699999999998</v>
       </c>
       <c r="D162" s="1">
-        <f t="shared" ref="D162:D183" si="20">100*(B162-C162)/C162</f>
+        <f t="shared" ref="D162:D185" si="20">100*(B162-C162)/C162</f>
         <v>-2.1396062085382019</v>
       </c>
       <c r="E162" s="1">
@@ -4929,6 +4932,48 @@
       </c>
       <c r="F183" s="1" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" ht="15.6">
+      <c r="A184" s="5">
+        <v>20260603</v>
+      </c>
+      <c r="B184">
+        <v>2126.107</v>
+      </c>
+      <c r="C184" s="1">
+        <v>2224.4699999999998</v>
+      </c>
+      <c r="D184" s="1">
+        <f t="shared" si="20"/>
+        <v>-4.4218622862974026</v>
+      </c>
+      <c r="E184" s="1">
+        <v>180</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" ht="15.6">
+      <c r="A185" s="5">
+        <v>20260603</v>
+      </c>
+      <c r="B185">
+        <v>2233.8420000000001</v>
+      </c>
+      <c r="C185" s="1">
+        <v>2224.4699999999998</v>
+      </c>
+      <c r="D185" s="1">
+        <f t="shared" si="20"/>
+        <v>0.42131384104979158</v>
+      </c>
+      <c r="E185" s="1">
+        <v>180</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
